--- a/naver-place-crawler/results_hair/일산_미용실.xlsx
+++ b/naver-place-crawler/results_hair/일산_미용실.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>러블리헤어 백석점</t>
+          <t>어반트랜드 대화점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lovelyhair81@naver.com</t>
+          <t>wkdsk161@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1310-9994</t>
+          <t>0507-1312-1997</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백석로71번길 39 1층 Lovely hair</t>
+          <t>경기도 고양시 일산서구 일산로636번길 7-10 1층 어반트랜드 대화점</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lovelyhair81</t>
+          <t>https://www.instagram.com/urbantrend_daehwa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>977</v>
+        <v>1559</v>
       </c>
       <c r="Q2" t="n">
-        <v>125</v>
+        <v>2534</v>
       </c>
       <c r="R2" t="n">
-        <v>1102</v>
+        <v>4093</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1537630018</t>
+          <t>1805638401</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537630018</t>
+          <t>https://m.place.naver.com/place/1805638401</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>씨엘로 헤어</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>choisucki@naver.com</t>
-        </is>
-      </c>
+          <t>이철헤어커커 일산역점</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1348-5733</t>
+          <t>0507-1367-3175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 대산로11번길 23-11 1층 씨엘로 헤어</t>
+          <t>경기도 고양시 일산서구 고양대로632번길 62 서원빌딩 2층 이철헤어커커</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/choisucki</t>
+          <t>https://www.instagram.com/kerker3175?igsh=bjNmOXZ5eXhybzh4&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +691,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +711,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>363</v>
+        <v>1935</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="R3" t="n">
-        <v>425</v>
+        <v>2012</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1188912062</t>
+          <t>1225883043</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1188912062</t>
+          <t>https://m.place.naver.com/place/1225883043</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>이철헤어커커 일산식사점</t>
+          <t>오위드 헤어</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>leechul4545@naver.com</t>
+          <t>sehwa_00@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1329-6367</t>
+          <t>0507-1381-8668</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 6 더 파인빌딩 301호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 제2층 B동-235호, B동-236호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://leechulhairkerker.co.kr</t>
+          <t>https://www.instagram.com/o.we.d_sehwa/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +805,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1709</v>
+        <v>725</v>
       </c>
       <c r="Q4" t="n">
-        <v>656</v>
+        <v>126</v>
       </c>
       <c r="R4" t="n">
-        <v>2365</v>
+        <v>851</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +820,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1872684285</t>
+          <t>1520474635</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1872684285</t>
+          <t>https://m.place.naver.com/place/1520474635</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -846,44 +842,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>아이디헤어 백마점</t>
+          <t>순수 일산라페스타점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dkfmadl6081@naver.com</t>
+          <t>juu1730@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1336-7632</t>
+          <t>0507-1429-7926</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 219 1층 아이디헤어 백마점</t>
+          <t>경기도 고양시 일산동구 무궁화로 32-12 라페스타 E동 203호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://idhairbm.quv.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,17 +895,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3729</v>
+        <v>2427</v>
       </c>
       <c r="Q5" t="n">
-        <v>388</v>
+        <v>492</v>
       </c>
       <c r="R5" t="n">
-        <v>4117</v>
+        <v>2919</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +914,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1226271832</t>
+          <t>1488039019</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1226271832</t>
+          <t>https://m.place.naver.com/place/1488039019</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -940,44 +936,48 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>보히니헤어 덕이점</t>
+          <t>아이디헤어 위시티점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bohinjhair@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>kwon_yummy@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>idhairkorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>031-913-1201</t>
+          <t>0507-1350-2540</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크로 141 2층(덕이동)</t>
+          <t>경기도 고양시 일산동구 위시티로 81 풍산트윈시티 2동 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bohinjhair</t>
+          <t>http://www.idhair.com</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2616</v>
+        <v>3898</v>
       </c>
       <c r="Q6" t="n">
-        <v>81</v>
+        <v>721</v>
       </c>
       <c r="R6" t="n">
-        <v>2697</v>
+        <v>4619</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1682988721</t>
+          <t>20342981</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682988721</t>
+          <t>https://m.place.naver.com/place/20342981</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 스타필드마켓 일산점</t>
+          <t>가로수헤어</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pscnetworks@naver.com</t>
+          <t>dbwl100420@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1386-2577</t>
+          <t>0507-1314-6708</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 171 스타필드마켓 일산점 지하2층</t>
+          <t>경기도 고양시 일산서구 주엽로 80 2층 c224호, c225호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pscnetworks</t>
+          <t>https://blog.naver.com/dbwl100420</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2427</v>
+        <v>4504</v>
       </c>
       <c r="Q7" t="n">
-        <v>96</v>
+        <v>143</v>
       </c>
       <c r="R7" t="n">
-        <v>2523</v>
+        <v>4647</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>37779126</t>
+          <t>1730294424</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37779126</t>
+          <t>https://m.place.naver.com/place/1730294424</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1128,25 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>브래뉴헤어 제니스점</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>유일헤어</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>simi_@naver.com</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1358-9247</t>
+          <t>0507-1462-7992</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 두산 위브더 제니스상가 1층 115,116호</t>
+          <t>경기도 고양시 일산서구 호수로 817 레이킨스몰 2층 259호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/branuhair_edge_t/?igshid=MzRlODBiNWFlZA%3D%3D</t>
+          <t>https://www.instagram.com/uil_purple</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>7287</v>
+        <v>986</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="R8" t="n">
-        <v>7391</v>
+        <v>1057</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>35848839</t>
+          <t>1980491932</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35848839</t>
+          <t>https://m.place.naver.com/place/1980491932</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1218,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>브래뉴헤어 중산점</t>
+          <t>메이원헤어 웨스턴돔점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>branu1842@naver.com</t>
+          <t>modeilsan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1371-5315</t>
+          <t>0507-1459-8857</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 60 일산아이파크2차 지하1층 108호</t>
+          <t>경기도 고양시 일산동구 정발산로 27 306호, 307호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/branu1842</t>
+          <t>https://www.instagram.com/may.one_ilsan.wd</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1255,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3099</v>
+        <v>1352</v>
       </c>
       <c r="Q9" t="n">
-        <v>126</v>
+        <v>395</v>
       </c>
       <c r="R9" t="n">
-        <v>3225</v>
+        <v>1747</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1218844742</t>
+          <t>1543258765</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1218844742</t>
+          <t>https://m.place.naver.com/place/1543258765</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1312,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 뉴코아아울렛 일산점</t>
+          <t>보그헤어 위시티점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dkqqk16@naver.com</t>
+          <t>vog_wicity@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1337-9452</t>
+          <t>0507-1317-3487</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 45 상가 B동 210호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/vog_wicity</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,12 +1348,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1365,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1358</v>
+        <v>1659</v>
       </c>
       <c r="Q10" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="R10" t="n">
-        <v>1541</v>
+        <v>1845</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>35734362</t>
+          <t>1668585644</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35734362</t>
+          <t>https://m.place.naver.com/place/1668585644</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>디얼스 킨텍스점</t>
+          <t>인생미용실</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dears5326@naver.com</t>
+          <t>simeon49@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-5326</t>
+          <t>0507-1340-0610</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 80 1층 C116호, C117호, C137호</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-11 라페스타 F동 215호 인생미용실</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://www.mydears.kr</t>
+          <t>https://hairshop.kakao.com/shops/4624</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,12 +1442,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>10252</v>
+        <v>4486</v>
       </c>
       <c r="Q11" t="n">
-        <v>2700</v>
+        <v>231</v>
       </c>
       <c r="R11" t="n">
-        <v>12952</v>
+        <v>4717</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1156337940</t>
+          <t>1743418994</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1156337940</t>
+          <t>https://m.place.naver.com/place/1743418994</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1500,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아이디헤어 웨스턴1호점</t>
+          <t>로이드밤 일산주엽역점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>idwd1@naver.com</t>
+          <t>zldektha@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1338-1654</t>
+          <t>031-916-8811</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 2층 아이디헤어 웨스턴1호점</t>
+          <t>경기도 고양시 일산서구 강성로 121 일산삼희프라자</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idwd1</t>
+          <t>http://www.lloydbomb.com/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1548,7 +1552,7 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>16053</v>
+        <v>4592</v>
       </c>
       <c r="Q12" t="n">
-        <v>2722</v>
+        <v>61</v>
       </c>
       <c r="R12" t="n">
-        <v>18775</v>
+        <v>4653</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1576,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>33664974</t>
+          <t>83137347</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33664974</t>
+          <t>https://m.place.naver.com/place/83137347</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1651,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1438</v>
+        <v>1455</v>
       </c>
       <c r="Q13" t="n">
-        <v>809</v>
+        <v>718</v>
       </c>
       <c r="R13" t="n">
-        <v>2247</v>
+        <v>2173</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1676,7 +1680,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1688,39 +1692,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>준오헤어 고양터미널점</t>
+          <t>아이디헤어 라페스타점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>munhyebin3787@naver.com</t>
+          <t>raziel-@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1409-7525</t>
+          <t>0507-1374-0041</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1036 지하1층</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 60-30 라페스타 B동 3F 315호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1741,17 +1745,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>14368</v>
+        <v>6782</v>
       </c>
       <c r="Q14" t="n">
-        <v>1074</v>
+        <v>1300</v>
       </c>
       <c r="R14" t="n">
-        <v>15442</v>
+        <v>8082</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1760,17 +1764,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>37865008</t>
+          <t>11893440</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37865008</t>
+          <t>https://m.place.naver.com/place/11893440</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1782,29 +1786,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>디자인바이문</t>
+          <t>바네헤어 일산웨스턴돔점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mgy64622@naver.com</t>
+          <t>banaehair_minji@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1386-0315</t>
+          <t>0507-1493-1378</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 호수로 688 코오롱레이크폴리스2차, B동 108호 디자인바이문</t>
+          <t>경기도 고양시 일산동구 정발산로 31-17 203호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/banaehair_minji</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1814,12 +1818,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1835,17 +1839,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3151</v>
+        <v>786</v>
       </c>
       <c r="Q15" t="n">
-        <v>614</v>
+        <v>1818</v>
       </c>
       <c r="R15" t="n">
-        <v>3765</v>
+        <v>2604</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1854,17 +1858,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1931662365</t>
+          <t>1566082176</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1931662365</t>
+          <t>https://m.place.naver.com/place/1566082176</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1876,29 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>아이디헤어 덕이점</t>
+          <t>하울 바이 아이디헤어</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0979012@naver.com</t>
+          <t>jhjung1128@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1477-3303</t>
+          <t>0507-1348-3312</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 하이파크3로 84 신성프라자 2층</t>
+          <t>경기도 고양시 일산동구 고양대로1021번길 33 스타타워3차 204호</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/0979012</t>
+          <t>https://www.instagram.com/haul_by_official</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1913,7 +1917,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1933,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>6355</v>
+        <v>6942</v>
       </c>
       <c r="Q16" t="n">
-        <v>781</v>
+        <v>2262</v>
       </c>
       <c r="R16" t="n">
-        <v>7136</v>
+        <v>9204</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1948,17 +1952,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1067110565</t>
+          <t>1112359679</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1067110565</t>
+          <t>https://m.place.naver.com/place/1112359679</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -1970,39 +1974,43 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>아이디헤어 주엽2호점</t>
+          <t>아이디헤어 주엽1호점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>p2464610@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>idhairjy1@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>idhairkorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1334-6477</t>
+          <t>0507-1353-2131</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 3층</t>
+          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 2층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/p2464610</t>
+          <t>http://www.idhair.com/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2027,13 +2035,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13612</v>
+        <v>8676</v>
       </c>
       <c r="Q17" t="n">
-        <v>5028</v>
+        <v>1929</v>
       </c>
       <c r="R17" t="n">
-        <v>18640</v>
+        <v>10605</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,17 +2050,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13321073</t>
+          <t>13342381</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13321073</t>
+          <t>https://m.place.naver.com/place/13342381</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2064,34 +2072,34 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아이디헤어 웨스턴2호점</t>
+          <t>준오헤어 가든웨스턴돔점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>idhairw002@naver.com</t>
+          <t>uzuworld@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>031-907-0022</t>
+          <t>031-931-6050</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1 A동 상가 4층 401호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idhairw002</t>
+          <t>http://junohair.com/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2101,7 +2109,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2121,13 +2129,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>21435</v>
+        <v>3659</v>
       </c>
       <c r="Q18" t="n">
-        <v>2128</v>
+        <v>204</v>
       </c>
       <c r="R18" t="n">
-        <v>23563</v>
+        <v>3863</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,17 +2144,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>13140579</t>
+          <t>31554365</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13140579</t>
+          <t>https://m.place.naver.com/place/31554365</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2158,29 +2166,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>어오즈</t>
+          <t>헤어샵 우연</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>icansangsu@naver.com</t>
+          <t>wy_hair@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1387-0718</t>
+          <t>0507-1439-2443</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로635번길 8-2 어오즈</t>
+          <t>경기도 고양시 일산동구 정발산로42번길 60 '웨스턴853 오피스텔' 213호</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/a.os_soo</t>
+          <t>https://blog.naver.com/wy_hair</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2195,7 +2203,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2211,17 +2219,17 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2133</v>
+        <v>191</v>
       </c>
       <c r="Q19" t="n">
-        <v>475</v>
+        <v>43</v>
       </c>
       <c r="R19" t="n">
-        <v>2608</v>
+        <v>234</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,17 +2238,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1161799656</t>
+          <t>2003326818</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1161799656</t>
+          <t>https://m.place.naver.com/place/2003326818</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2252,29 +2260,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>붙임머리 더오르 일산점</t>
+          <t>신승원컷앤컷 붙임머리 일산점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>theorr13@naver.com</t>
+          <t>yamano86@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1481-8344</t>
+          <t>0507-1439-7962</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층 417호</t>
+          <t>경기도 고양시 일산동구 백마로213번길 36 1층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/theorr13</t>
+          <t>https://blog.naver.com/yamano86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2305,17 +2313,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>618</v>
+        <v>1586</v>
       </c>
       <c r="Q20" t="n">
-        <v>481</v>
+        <v>405</v>
       </c>
       <c r="R20" t="n">
-        <v>1099</v>
+        <v>1991</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2324,17 +2332,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1697779011</t>
+          <t>34907119</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697779011</t>
+          <t>https://m.place.naver.com/place/34907119</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2346,29 +2354,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>라니지헤어</t>
+          <t>준오헤어 원마운트 스트리트점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dain582269@naver.com</t>
+          <t>babotenggu@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1340-9985</t>
+          <t>0507-1307-6560</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 210호</t>
+          <t>경기도 고양시 일산서구 한류월드로 300 원마운트 1층 1027호</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/raniji_hair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2378,7 +2386,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2399,17 +2407,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>845</v>
+        <v>8919</v>
       </c>
       <c r="Q21" t="n">
-        <v>64</v>
+        <v>631</v>
       </c>
       <c r="R21" t="n">
-        <v>909</v>
+        <v>9550</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,17 +2426,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1197147374</t>
+          <t>1870990318</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197147374</t>
+          <t>https://m.place.naver.com/place/1870990318</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2440,29 +2448,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>제니스튜디오 일산식사점</t>
+          <t>브래뉴헤어 제니스점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tmfal0808@naver.com</t>
+          <t>ysdcj@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>031-968-4163</t>
+          <t>0507-1358-9247</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 55-2 1층, 2층</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 두산 위브더 제니스상가 1층 115,116호</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jennystudio_ilsan</t>
+          <t>https://www.instagram.com/branuhair_edge_t/?igshid=MzRlODBiNWFlZA%3D%3D</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2497,13 +2505,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1825</v>
+        <v>7348</v>
       </c>
       <c r="Q22" t="n">
-        <v>166</v>
+        <v>105</v>
       </c>
       <c r="R22" t="n">
-        <v>1991</v>
+        <v>7453</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2512,17 +2520,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1625300615</t>
+          <t>35848839</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625300615</t>
+          <t>https://m.place.naver.com/place/35848839</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2534,25 +2542,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>씨무드헤어</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>박승철헤어스투디오 뉴코아아울렛 일산점</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>dkqqk16@naver.com</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1309-3512</t>
+          <t>0507-1337-9452</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 38 2층 204호</t>
+          <t>경기도 고양시 일산동구 중앙로 1206 뉴코아아울렛 9층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/c_mood.hair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2562,7 +2574,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2583,17 +2595,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>639</v>
+        <v>1361</v>
       </c>
       <c r="Q23" t="n">
-        <v>230</v>
+        <v>183</v>
       </c>
       <c r="R23" t="n">
-        <v>869</v>
+        <v>1544</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2602,17 +2614,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1511035217</t>
+          <t>35734362</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1511035217</t>
+          <t>https://m.place.naver.com/place/35734362</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2624,29 +2636,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>로미르헤어</t>
+          <t>브래뉴헤어 중산점</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>romir_hair@naver.com</t>
+          <t>branu1842@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1423-0963</t>
+          <t>0507-1371-5315</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 45 B동 2층 217호</t>
+          <t>경기도 고양시 일산동구 중산로 60 일산아이파크2차 지하1층 108호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/romir_hair</t>
+          <t>https://blog.naver.com/branu1842</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2677,17 +2689,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>833</v>
+        <v>3114</v>
       </c>
       <c r="Q24" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="R24" t="n">
-        <v>922</v>
+        <v>3240</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2696,17 +2708,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1442538783</t>
+          <t>1218844742</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1442538783</t>
+          <t>https://m.place.naver.com/place/1218844742</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2718,34 +2730,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>레브로미</t>
+          <t>담따 일산킨텍스점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>yeonxji@naver.com</t>
+          <t>didamda01@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1370-9230</t>
+          <t>0507-1347-3331</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 태극로 11 한류월드 유보라 더 스마트 101동 상가 1층 125호</t>
+          <t>경기도 고양시 일산서구 킨텍스로 240 꿈에그린 GIFC 몰 지하1층 B159 담따</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reve_yeonji</t>
+          <t>http://www.instagram.com/damdda_official</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2755,7 +2767,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2775,13 +2787,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2498</v>
+        <v>4804</v>
       </c>
       <c r="Q25" t="n">
-        <v>2167</v>
+        <v>5333</v>
       </c>
       <c r="R25" t="n">
-        <v>4665</v>
+        <v>10137</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2790,17 +2802,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1728357195</t>
+          <t>1701230993</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1728357195</t>
+          <t>https://m.place.naver.com/place/1701230993</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2812,29 +2824,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>준오헤어 가든 원마운트</t>
+          <t>준오헤어 일산 웨스턴돔2호점</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2wnsgod2@naver.com</t>
+          <t>jennyjjinny@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1325-6505</t>
+          <t>0507-1425-0605</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 한류월드로 300 원마운트 2층 2067호 준오헤어 가든 원마운트</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 254호</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juno_onemount.garden</t>
+          <t>https://www.instagram.com/juno_iw2</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2869,13 +2881,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>9543</v>
+        <v>9325</v>
       </c>
       <c r="Q26" t="n">
-        <v>1470</v>
+        <v>387</v>
       </c>
       <c r="R26" t="n">
-        <v>11013</v>
+        <v>9712</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2884,17 +2896,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>32307986</t>
+          <t>34974777</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32307986</t>
+          <t>https://m.place.naver.com/place/34974777</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -2906,29 +2918,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SUPHAIR 일산킨텍스 본점</t>
+          <t>아이디헤어 웨스턴2호점</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>shffkwyd@naver.com</t>
+          <t>idhairw002@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1375-1104</t>
+          <t>031-907-0022</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC MALL 지하1층 b154호,155호</t>
+          <t>경기도 고양시 일산동구 정발산로 23 호수빌딩 2층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_sup_1104</t>
+          <t>https://blog.naver.com/idhairw002</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2943,7 +2955,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2963,13 +2975,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2451</v>
+        <v>21488</v>
       </c>
       <c r="Q27" t="n">
-        <v>211</v>
+        <v>2141</v>
       </c>
       <c r="R27" t="n">
-        <v>2662</v>
+        <v>23629</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2978,17 +2990,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1778930095</t>
+          <t>13140579</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1778930095</t>
+          <t>https://m.place.naver.com/place/13140579</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3000,44 +3012,48 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>가로수헤어</t>
+          <t>오캄 현대백화점 킨텍스점</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dbwl100420@naver.com</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>lovingly_@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>akh@smartplug.kr</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0507-1314-6708</t>
+          <t>0507-1374-3975</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 80 2층 c224호, c225호</t>
+          <t>경기도 고양시 일산서구 호수로 817 현대백화점 9층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dbwl100420</t>
+          <t>https://booking.naver.com/booking/13/bizes/262734</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3053,17 +3069,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>4498</v>
+        <v>17520</v>
       </c>
       <c r="Q28" t="n">
-        <v>145</v>
+        <v>275</v>
       </c>
       <c r="R28" t="n">
-        <v>4643</v>
+        <v>17795</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3072,17 +3088,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1730294424</t>
+          <t>1448172220</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730294424</t>
+          <t>https://m.place.naver.com/place/1448172220</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3094,29 +3110,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>박승철 헤어스투디오 백마점</t>
+          <t>올하나헤어</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>pschairbaengma@naver.com</t>
+          <t>oll1hair@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1381-5735</t>
+          <t>0507-1344-6507</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 208 한일빌딩 201호</t>
+          <t>경기도 고양시 일산동구 태극로 11 반도유보라 상가 102동 1층 152, 3, 4,호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pschairbaengma</t>
+          <t>https://blog.naver.com/oll1hair</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3147,17 +3163,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3548</v>
+        <v>1931</v>
       </c>
       <c r="Q29" t="n">
-        <v>315</v>
+        <v>2631</v>
       </c>
       <c r="R29" t="n">
-        <v>3863</v>
+        <v>4562</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3166,17 +3182,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1583990490</t>
+          <t>1636578210</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1583990490</t>
+          <t>https://m.place.naver.com/place/1636578210</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3188,39 +3204,43 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>헤어레스트지오 탄현점</t>
+          <t>프리미엄 이가자 일산차병원점</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hairrestzio@naver.com</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>lkj_ilsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1349-9336</t>
+          <t>0507-1312-8374</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 48 현해프라자 2층</t>
+          <t>경기도 고양시 일산동구 중앙로 1205 301호 일부(장항동, 차움 라이프센터)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hairrestzio</t>
+          <t>http://booking.naver.com/booking/13/bizes/1155462</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3245,13 +3265,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2753</v>
+        <v>4467</v>
       </c>
       <c r="Q30" t="n">
-        <v>380</v>
+        <v>842</v>
       </c>
       <c r="R30" t="n">
-        <v>3133</v>
+        <v>5309</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3260,17 +3280,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>20557893</t>
+          <t>1278204022</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/20557893</t>
+          <t>https://m.place.naver.com/place/1278204022</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3282,29 +3302,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>헤어어노즈 일산킨텍스점</t>
+          <t>아이디헤어 웨스턴1호점</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lifeisyum@naver.com</t>
+          <t>idwd1@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1368-2999</t>
+          <t>0507-1338-1654</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 월드고양로 21 원시티상가 1층 339호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 2층 아이디헤어 웨스턴1호점</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/anoz_hy</t>
+          <t>https://blog.naver.com/idwd1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3319,7 +3339,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3339,13 +3359,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2229</v>
+        <v>16102</v>
       </c>
       <c r="Q31" t="n">
-        <v>1042</v>
+        <v>2740</v>
       </c>
       <c r="R31" t="n">
-        <v>3271</v>
+        <v>18842</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3354,17 +3374,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1962297568</t>
+          <t>33664974</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1962297568</t>
+          <t>https://m.place.naver.com/place/33664974</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3376,44 +3396,44 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>헤어온새</t>
+          <t>디얼스 백석벨라시타점</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4h14m@naver.com</t>
+          <t>qgzbasqda@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1409-3382</t>
+          <t>0507-1320-0920</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 3 B101호 헤어온새</t>
+          <t>경기도 고양시 일산동구 강송로 33 2층 A2108호</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://mydears.kr</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3429,17 +3449,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>959</v>
+        <v>651</v>
       </c>
       <c r="Q32" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="R32" t="n">
-        <v>1038</v>
+        <v>732</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3448,17 +3468,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1869648797</t>
+          <t>2061248214</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1869648797</t>
+          <t>https://m.place.naver.com/place/2061248214</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3470,29 +3490,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>리안헤어 주엽역점</t>
+          <t>리안헤어 일산백마대로점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>joriahn2018@naver.com</t>
+          <t>swtysa12_@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0507-1435-6063</t>
+          <t>031-906-6661</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1470 동부썬프라자 A동 2층 리안헤어</t>
+          <t>경기도 고양시 일산동구 일산로 247 2층 리안헤어 일산백마대로점</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/joriahn2018</t>
+          <t>https://blog.naver.com/swtysa12_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3527,13 +3547,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3575</v>
+        <v>8165</v>
       </c>
       <c r="Q33" t="n">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="R33" t="n">
-        <v>3914</v>
+        <v>8470</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3542,17 +3562,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1116048605</t>
+          <t>1838625457</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1116048605</t>
+          <t>https://m.place.naver.com/place/1838625457</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3564,25 +3584,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>헤어하우스나인원</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>붙임머리 더오르 일산점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>theorr13@naver.com</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1384-1654</t>
+          <t>0507-1481-8344</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로 666 상가 D동 209호</t>
+          <t>경기도 고양시 일산동구 정발산로 43-20 센트럴프라자 4층 417호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/theorr13</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3592,12 +3616,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3613,17 +3637,17 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1564</v>
+        <v>637</v>
       </c>
       <c r="Q34" t="n">
-        <v>2907</v>
+        <v>487</v>
       </c>
       <c r="R34" t="n">
-        <v>4471</v>
+        <v>1124</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3632,17 +3656,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1664556396</t>
+          <t>1697779011</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664556396</t>
+          <t>https://m.place.naver.com/place/1697779011</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3657,11 +3681,7 @@
           <t>메종드 아이디헤어 백석벨라시타점</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>leave35@naver.com</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
@@ -3711,13 +3731,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>10300</v>
+        <v>10316</v>
       </c>
       <c r="Q35" t="n">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="R35" t="n">
-        <v>11974</v>
+        <v>11992</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3736,7 +3756,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3748,29 +3768,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>더감각헤어 백석점</t>
+          <t>리안헤어 주엽역점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>thegamgak_@naver.com</t>
+          <t>joriahn2018@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1341-2949</t>
+          <t>0507-1435-6063</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자 3차 206호</t>
+          <t>경기도 고양시 일산서구 중앙로 1470 동부썬프라자 A동 2층 리안헤어</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/thegamgak_</t>
+          <t>https://blog.naver.com/joriahn2018</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3801,17 +3821,17 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1210</v>
+        <v>3590</v>
       </c>
       <c r="Q36" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="R36" t="n">
-        <v>1588</v>
+        <v>3932</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3820,17 +3840,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1088474581</t>
+          <t>1116048605</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088474581</t>
+          <t>https://m.place.naver.com/place/1116048605</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3842,29 +3862,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>바네헤어 일산웨스턴돔점</t>
+          <t>이철헤어커커 백석점</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>banaehair_minji@naver.com</t>
+          <t>tmdwn363@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1493-1378</t>
+          <t>0507-1485-2331</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-17 203호</t>
+          <t>경기도 고양시 일산동구 중앙로 1079 백석 더리브스타일 2층 212호~215호</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/banaehair_minji</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3874,12 +3894,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3895,17 +3915,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>772</v>
+        <v>4885</v>
       </c>
       <c r="Q37" t="n">
-        <v>1729</v>
+        <v>238</v>
       </c>
       <c r="R37" t="n">
-        <v>2501</v>
+        <v>5123</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3914,17 +3934,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1566082176</t>
+          <t>1363009552</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1566082176</t>
+          <t>https://m.place.naver.com/place/1363009552</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -3936,39 +3956,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>오캄 현대백화점 킨텍스점</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>akh@smartplug.kr</t>
-        </is>
-      </c>
+          <t>라프네 AVEDA 컨셉 살롱</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>lafne-aveda@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1374-3975</t>
+          <t>0507-1309-5429</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 현대백화점 9층</t>
+          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬 4층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/262734</t>
+          <t>https://www.instagram.com/lafne_aveda</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3989,17 +4009,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>17209</v>
+        <v>2492</v>
       </c>
       <c r="Q38" t="n">
-        <v>275</v>
+        <v>2096</v>
       </c>
       <c r="R38" t="n">
-        <v>17484</v>
+        <v>4588</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4008,17 +4028,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1448172220</t>
+          <t>1456773923</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1448172220</t>
+          <t>https://m.place.naver.com/place/1456773923</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4030,29 +4050,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>메종드아이디헤어 위시티점 1관</t>
+          <t>라니지헤어</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>idhair01199@naver.com</t>
+          <t>dain582269@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1408-1654</t>
+          <t>0507-1340-9985</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워1차 2층 아이디헤어</t>
+          <t>경기도 고양시 일산동구 무궁화로 20-38 로데오탑 210호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/idhair_wicity_official</t>
+          <t>https://www.instagram.com/raniji_hair</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4087,13 +4107,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3759</v>
+        <v>852</v>
       </c>
       <c r="Q39" t="n">
-        <v>1460</v>
+        <v>65</v>
       </c>
       <c r="R39" t="n">
-        <v>5219</v>
+        <v>917</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4102,17 +4122,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>35862167</t>
+          <t>1197147374</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35862167</t>
+          <t>https://m.place.naver.com/place/1197147374</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4124,29 +4144,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>올하나헤어</t>
+          <t>헤어온새</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>oll1hair@naver.com</t>
+          <t>4h14m@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1344-6507</t>
+          <t>0507-1409-3382</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 태극로 11 반도유보라 상가 102동 1층 152, 3, 4,호</t>
+          <t>경기도 고양시 일산동구 중산로 3 B101호 헤어온새</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/oll1hair</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4156,12 +4176,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4177,17 +4197,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1922</v>
+        <v>983</v>
       </c>
       <c r="Q40" t="n">
-        <v>2458</v>
+        <v>82</v>
       </c>
       <c r="R40" t="n">
-        <v>4380</v>
+        <v>1065</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4196,17 +4216,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1636578210</t>
+          <t>1869648797</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636578210</t>
+          <t>https://m.place.naver.com/place/1869648797</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4218,34 +4238,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>어반트랜드 대화점</t>
+          <t>아이디헤어 백마점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>wkdsk161@naver.com</t>
+          <t>imraina@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1312-1997</t>
+          <t>0507-1336-7632</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로636번길 7-10 1층 어반트랜드 대화점</t>
+          <t>경기도 고양시 일산동구 일산로 219 1층 아이디헤어 백마점</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/urbantrend_daehwa</t>
+          <t>https://idhairbm.quv.kr/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4255,7 +4275,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4275,13 +4295,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1521</v>
+        <v>3748</v>
       </c>
       <c r="Q41" t="n">
-        <v>2607</v>
+        <v>389</v>
       </c>
       <c r="R41" t="n">
-        <v>4128</v>
+        <v>4137</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4290,17 +4310,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1805638401</t>
+          <t>1226271832</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1805638401</t>
+          <t>https://m.place.naver.com/place/1226271832</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4312,29 +4332,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>헤어디자인 상상 2호점</t>
+          <t>준오헤어 가든 원마운트</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>assa807@naver.com</t>
+          <t>2wnsgod2@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>031-903-7897</t>
+          <t>0507-1325-6505</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로88번길 8-6 1층</t>
+          <t>경기도 고양시 일산서구 한류월드로 300 원마운트 2층 2067호 준오헤어 가든 원마운트</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kangkang2_2</t>
+          <t>https://www.instagram.com/juno_onemount.garden</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4369,13 +4389,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>850</v>
+        <v>9767</v>
       </c>
       <c r="Q42" t="n">
-        <v>143</v>
+        <v>1494</v>
       </c>
       <c r="R42" t="n">
-        <v>993</v>
+        <v>11261</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4384,17 +4404,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>611759293</t>
+          <t>32307986</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/611759293</t>
+          <t>https://m.place.naver.com/place/32307986</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4406,25 +4426,29 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>이철헤어커커 백석점</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>스페셜아이디헤어 웨스턴돔점</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sid9315011@naver.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0507-1485-2331</t>
+          <t>0507-1485-5011</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1079 백석 더리브스타일 2층 212호~215호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔I동 2층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sid9315011</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4434,12 +4458,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4459,13 +4483,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>4859</v>
+        <v>3679</v>
       </c>
       <c r="Q43" t="n">
-        <v>238</v>
+        <v>1117</v>
       </c>
       <c r="R43" t="n">
-        <v>5097</v>
+        <v>4796</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4474,17 +4498,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1363009552</t>
+          <t>19542744</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1363009552</t>
+          <t>https://m.place.naver.com/place/19542744</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4496,25 +4520,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>순수 일산라페스타점</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>보히니헤어 덕이점</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>bohinjhair@naver.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1429-7926</t>
+          <t>031-913-1201</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 32-12 라페스타 E동 203호</t>
+          <t>경기도 고양시 일산서구 하이파크로 141 2층(덕이동)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/bohinjhair</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4524,7 +4552,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -4545,17 +4573,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2391</v>
+        <v>2625</v>
       </c>
       <c r="Q44" t="n">
-        <v>433</v>
+        <v>81</v>
       </c>
       <c r="R44" t="n">
-        <v>2824</v>
+        <v>2706</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,17 +4592,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1488039019</t>
+          <t>1682988721</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1488039019</t>
+          <t>https://m.place.naver.com/place/1682988721</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4586,34 +4614,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>오브르헤어 본점</t>
+          <t>디얼스 킨텍스점</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>bellentkdwo3@naver.com</t>
+          <t>dears5326@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0507-1422-0397</t>
+          <t>0507-1360-5326</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 31-10 파크프라자 205호</t>
+          <t>경기도 고양시 일산서구 주엽로 80 1층 C116호, C117호, C137호</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ssangj_ab</t>
+          <t>http://www.mydears.kr</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4623,7 +4651,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4643,13 +4671,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>593</v>
+        <v>10318</v>
       </c>
       <c r="Q45" t="n">
-        <v>496</v>
+        <v>2740</v>
       </c>
       <c r="R45" t="n">
-        <v>1089</v>
+        <v>13058</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,17 +4686,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1907719129</t>
+          <t>1156337940</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1907719129</t>
+          <t>https://m.place.naver.com/place/1156337940</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4680,29 +4708,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>뮤트헤어</t>
+          <t>루나준헤어</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mute91-@naver.com</t>
+          <t>hyuneedaa@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1356-0736</t>
+          <t>031-922-1654</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 528 신문화빌딩 201호</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 위브더제니스 1층 루나준헤어</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mute91-</t>
+          <t>https://www.instagram.com/lunajunhair</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4717,7 +4745,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4737,13 +4765,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>270</v>
+        <v>425</v>
       </c>
       <c r="Q46" t="n">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="R46" t="n">
-        <v>410</v>
+        <v>479</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4780,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1269262973</t>
+          <t>1880124000</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1269262973</t>
+          <t>https://m.place.naver.com/place/1880124000</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4774,34 +4802,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>디얼스 백석벨라시타점</t>
+          <t>바바헤어 웨스턴점</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wudaos123@naver.com</t>
+          <t>baba5232@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0507-1320-0920</t>
+          <t>0507-1315-5225</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 강송로 33 2층 A2108호</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://mydears.kr</t>
+          <t>https://blog.naver.com/baba5232</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4827,17 +4855,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>288</v>
+        <v>1091</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="R47" t="n">
-        <v>334</v>
+        <v>1110</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,17 +4874,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2061248214</t>
+          <t>38238744</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2061248214</t>
+          <t>https://m.place.naver.com/place/38238744</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4868,29 +4896,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>준오헤어 원마운트 스트리트점</t>
+          <t>살롱드마샬 웨스턴돔점</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>geoj1@naver.com</t>
+          <t>sweetjoo77@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1307-6560</t>
+          <t>031-931-5080</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 한류월드로 300 원마운트 1층 1027호</t>
+          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 1동 104호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/sweetjoo77</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4900,12 +4928,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4921,17 +4949,17 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>8882</v>
+        <v>1441</v>
       </c>
       <c r="Q48" t="n">
-        <v>627</v>
+        <v>97</v>
       </c>
       <c r="R48" t="n">
-        <v>9509</v>
+        <v>1538</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4968,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1870990318</t>
+          <t>13088695</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870990318</t>
+          <t>https://m.place.naver.com/place/13088695</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -4962,34 +4990,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>준오헤어 가든웨스턴돔점</t>
+          <t>어오즈</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>mydearestday@naver.com</t>
+          <t>icansangsu@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>031-931-6050</t>
+          <t>0507-1387-0718</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔1 A동 상가 4층 401호</t>
+          <t>경기도 고양시 일산서구 일산로635번길 8-2 어오즈</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://junohair.com/</t>
+          <t>https://www.instagram.com/a.os_soo</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5019,13 +5047,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3649</v>
+        <v>2155</v>
       </c>
       <c r="Q49" t="n">
-        <v>204</v>
+        <v>475</v>
       </c>
       <c r="R49" t="n">
-        <v>3853</v>
+        <v>2630</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,17 +5062,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>31554365</t>
+          <t>1161799656</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31554365</t>
+          <t>https://m.place.naver.com/place/1161799656</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5056,25 +5084,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>하울 바이 아이디헤어</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>누아헤어 킨텍스점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>artistheojun@naver.com</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1348-3312</t>
+          <t>0507-1368-6334</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 고양대로1021번길 33 스타타워3차 204호</t>
+          <t>경기도 고양시 일산서구 주엽로 80 (호수공원 가로수길 상가) A동 109, 110호</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/haul_by_official</t>
+          <t>https://blog.naver.com/artistheojun</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5089,7 +5121,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5109,13 +5141,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>6899</v>
+        <v>3344</v>
       </c>
       <c r="Q50" t="n">
-        <v>2228</v>
+        <v>140</v>
       </c>
       <c r="R50" t="n">
-        <v>9127</v>
+        <v>3484</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5124,17 +5156,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1112359679</t>
+          <t>1813401259</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1112359679</t>
+          <t>https://m.place.naver.com/place/1813401259</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5146,29 +5178,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>라프네 AVEDA 컨셉 살롱</t>
+          <t>이가자헤어비스 일산킨텍스홈플러스점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>lafne-aveda@naver.com</t>
+          <t>jsj_0409@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1309-5429</t>
+          <t>0507-1413-8322</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1261번길 55 효산캐슬 4층</t>
+          <t>경기도 고양시 일산서구 호수로 817 홈플러스 지하1층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lafne_aveda</t>
+          <t>https://blog.naver.com/jsj_0409</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5183,7 +5215,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5203,13 +5235,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2486</v>
+        <v>8384</v>
       </c>
       <c r="Q51" t="n">
-        <v>2199</v>
+        <v>911</v>
       </c>
       <c r="R51" t="n">
-        <v>4685</v>
+        <v>9295</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5250,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1456773923</t>
+          <t>37249308</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456773923</t>
+          <t>https://m.place.naver.com/place/37249308</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5240,29 +5272,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>이가자헤어비스 일산킨텍스홈플러스점</t>
+          <t>박승철헤어스투디오 탄현제니스점</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jsj_0409@naver.com</t>
+          <t>lojy0824@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1413-8322</t>
+          <t>0507-1365-1111</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 호수로 817 홈플러스 지하1층</t>
+          <t>경기도 고양시 일산서구 일현로 97-11 170호 박승철헤어 탄현제니스점</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jsj_0409</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5272,12 +5304,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5293,17 +5325,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>8348</v>
+        <v>697</v>
       </c>
       <c r="Q52" t="n">
-        <v>901</v>
+        <v>113</v>
       </c>
       <c r="R52" t="n">
-        <v>9249</v>
+        <v>810</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,17 +5344,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>37249308</t>
+          <t>2024760607</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37249308</t>
+          <t>https://m.place.naver.com/place/2024760607</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5334,29 +5366,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>메이원헤어 웨스턴돔점</t>
+          <t>에이바헤어 마두역점</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>modeilsan@naver.com</t>
+          <t>sakuraa88@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1459-8857</t>
+          <t>0507-1440-4564</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 27 306호, 307호</t>
+          <t>경기도 고양시 일산동구 장백로 184 2층 211호</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/may.one_ilsan.wd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5366,7 +5398,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5387,17 +5419,17 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1297</v>
+        <v>1925</v>
       </c>
       <c r="Q53" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="R53" t="n">
-        <v>1686</v>
+        <v>2317</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5438,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1543258765</t>
+          <t>1762602085</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1543258765</t>
+          <t>https://m.place.naver.com/place/1762602085</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5428,44 +5460,48 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>오위드 헤어</t>
+          <t>아이디헤어 원마운트점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sehwa_00@naver.com</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>throddl@naver.com</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>idhairkorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1381-8668</t>
+          <t>0507-1359-6700</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 제2층 B동-235호, B동-236호</t>
+          <t>경기도 고양시 일산서구 한류월드로 300 2층 아이디헤어 원마운트점</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/o.we.d_sehwa/</t>
+          <t>http://www.idhair.com</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5485,13 +5521,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>698</v>
+        <v>26836</v>
       </c>
       <c r="Q54" t="n">
-        <v>125</v>
+        <v>6629</v>
       </c>
       <c r="R54" t="n">
-        <v>823</v>
+        <v>33465</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,65 +5536,61 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1520474635</t>
+          <t>32630576</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1520474635</t>
+          <t>https://m.place.naver.com/place/32630576</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>남성전문미용실</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아이디헤어 주엽1호점</t>
+          <t>매일헤어 : Male Hair</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>idhairjy1@naver.com</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>idhairkorea@gmail.com</t>
-        </is>
-      </c>
+          <t>sindy_0329@naver.com</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1353-2131</t>
+          <t>0507-1351-5935</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1456 서현프라자 2층</t>
+          <t>경기도 고양시 일산동구 무궁화로 12 한라밀라트 C동 101호 매일헤어</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>http://www.idhair.com/</t>
+          <t>https://blog.naver.com/sindy_0329</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -5583,13 +5615,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>8610</v>
+        <v>870</v>
       </c>
       <c r="Q55" t="n">
-        <v>1847</v>
+        <v>11</v>
       </c>
       <c r="R55" t="n">
-        <v>10457</v>
+        <v>881</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5598,17 +5630,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>13342381</t>
+          <t>1751642688</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13342381</t>
+          <t>https://m.place.naver.com/place/1751642688</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5620,29 +5652,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>메종드아이디헤어 위시티점 2관</t>
+          <t>헤어하우스나인원</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>id_wicity2@naver.com</t>
+          <t>marlang2@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1359-1653</t>
+          <t>0507-1384-1654</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워1차 2층 메종드아이디헤어 위시티점 2관</t>
+          <t>경기도 고양시 일산서구 고양대로 666 상가 D동 209호</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/idhair_wicity_official</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5652,7 +5684,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5673,17 +5705,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3740</v>
+        <v>1606</v>
       </c>
       <c r="Q56" t="n">
-        <v>889</v>
+        <v>2933</v>
       </c>
       <c r="R56" t="n">
-        <v>4629</v>
+        <v>4539</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5692,17 +5724,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>804518540</t>
+          <t>1664556396</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/804518540</t>
+          <t>https://m.place.naver.com/place/1664556396</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5714,43 +5746,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>프리미엄 이가자 일산차병원점</t>
+          <t>더감각헤어 백석점</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>lkj_ilsan@naver.com</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>thegamgak_@naver.com</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1312-8374</t>
+          <t>0507-1341-2949</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1205 301호 일부(장항동, 차움 라이프센터)</t>
+          <t>경기도 고양시 일산동구 일산로 46 남정시티프라자 3차 206호</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://booking.naver.com/booking/13/bizes/1155462</t>
+          <t>https://blog.naver.com/thegamgak_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5771,17 +5799,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>4386</v>
+        <v>1233</v>
       </c>
       <c r="Q57" t="n">
-        <v>832</v>
+        <v>400</v>
       </c>
       <c r="R57" t="n">
-        <v>5218</v>
+        <v>1633</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5790,17 +5818,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1278204022</t>
+          <t>1088474581</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1278204022</t>
+          <t>https://m.place.naver.com/place/1088474581</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5812,44 +5840,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>준오헤어 일산 웨스턴돔2호점</t>
+          <t>이철헤어커커 일산식사점</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>mod0406@naver.com</t>
+          <t>leechul4545@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1425-0605</t>
+          <t>0507-1329-6367</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔 A동 2층 254호</t>
+          <t>경기도 고양시 일산동구 위시티로 6 더 파인빌딩 301호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/juno_iw2</t>
+          <t>https://leechulhairkerker.co.kr</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5860,7 +5888,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5869,13 +5897,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>9297</v>
+        <v>1715</v>
       </c>
       <c r="Q58" t="n">
-        <v>387</v>
+        <v>624</v>
       </c>
       <c r="R58" t="n">
-        <v>9684</v>
+        <v>2339</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5884,17 +5912,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>34974777</t>
+          <t>1872684285</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34974777</t>
+          <t>https://m.place.naver.com/place/1872684285</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -5906,24 +5934,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>박승철헤어스투디오 탄현제니스점</t>
+          <t>리안헤어 일산중산동점</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jjinsalagn@naver.com</t>
+          <t>wlsdudlover@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0507-1365-1111</t>
+          <t>031-977-3211</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 170호 박승철헤어 탄현제니스점</t>
+          <t>경기도 고양시 일산동구 중산로 67</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5963,13 +5991,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>589</v>
+        <v>3494</v>
       </c>
       <c r="Q59" t="n">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="R59" t="n">
-        <v>687</v>
+        <v>3524</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5978,17 +6006,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>2024760607</t>
+          <t>1780881257</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024760607</t>
+          <t>https://m.place.naver.com/place/1780881257</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6000,29 +6028,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>스페셜아이디헤어 웨스턴돔점</t>
+          <t>쓰담스타일을담다 일산점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sid9315011@naver.com</t>
+          <t>ssdam80@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1485-5011</t>
+          <t>0507-1360-3342</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 정발산로 24 웨스턴돔I동 2층</t>
+          <t>경기도 고양시 일산동구 정발산로 24 2층 A동 I-204호</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sid9315011</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6032,12 +6060,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6057,13 +6085,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3659</v>
+        <v>2867</v>
       </c>
       <c r="Q60" t="n">
-        <v>1069</v>
+        <v>158</v>
       </c>
       <c r="R60" t="n">
-        <v>4728</v>
+        <v>3025</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6072,17 +6100,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>19542744</t>
+          <t>1027530573</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19542744</t>
+          <t>https://m.place.naver.com/place/1027530573</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6094,29 +6122,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>신승원컷앤컷 붙임머리 일산점</t>
+          <t>에이치앤드</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>yamano86@naver.com</t>
+          <t>h_andofficial@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0507-1439-7962</t>
+          <t>0507-1360-9096</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 백마로213번길 36 1층</t>
+          <t>경기도 고양시 일산동구 정발산로 47 2층 211호, 211-1호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yamano86</t>
+          <t>https://www.instagram.com/h.andofficial</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6131,7 +6159,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6147,17 +6175,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1573</v>
+        <v>5266</v>
       </c>
       <c r="Q61" t="n">
-        <v>403</v>
+        <v>79</v>
       </c>
       <c r="R61" t="n">
-        <v>1976</v>
+        <v>5345</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6166,17 +6194,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>34907119</t>
+          <t>1530382831</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34907119</t>
+          <t>https://m.place.naver.com/place/1530382831</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6188,29 +6216,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>누아헤어 킨텍스점</t>
+          <t>루루제이 바이 아이디헤어</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>artistheojun@naver.com</t>
+          <t>idhairsuho@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1368-6334</t>
+          <t>0507-1381-3405</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 주엽로 80 (호수공원 가로수길 상가) A동 109, 110호</t>
+          <t>경기도 고양시 일산동구 중산로 63 4층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/artistheojun</t>
+          <t>https://blog.naver.com/idhairsuho</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6245,13 +6273,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3326</v>
+        <v>4591</v>
       </c>
       <c r="Q62" t="n">
-        <v>140</v>
+        <v>512</v>
       </c>
       <c r="R62" t="n">
-        <v>3466</v>
+        <v>5103</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6260,17 +6288,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1813401259</t>
+          <t>1598173425</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1813401259</t>
+          <t>https://m.place.naver.com/place/1598173425</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6282,29 +6310,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>담따 일산킨텍스점</t>
+          <t>텐파운드헤어 일산장항점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>didamda01@naver.com</t>
+          <t>tjcksqkf@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1347-3331</t>
+          <t>0507-1363-2782</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 꿈에그린 GIFC 몰 지하1층 B159 담따</t>
+          <t>경기도 고양시 일산동구 정발산로 47 205호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/damdda_official</t>
+          <t>https://blog.naver.com/tjcksqkf</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6319,7 +6347,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6339,13 +6367,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4794</v>
+        <v>16537</v>
       </c>
       <c r="Q63" t="n">
-        <v>5280</v>
+        <v>1301</v>
       </c>
       <c r="R63" t="n">
-        <v>10074</v>
+        <v>17838</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6354,17 +6382,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1701230993</t>
+          <t>1514577675</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1701230993</t>
+          <t>https://m.place.naver.com/place/1514577675</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6376,34 +6404,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>루루제이 바이 아이디헤어</t>
+          <t>준오헤어 고양터미널점</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>idhairsuho@naver.com</t>
+          <t>munhyebin3787@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1381-3405</t>
+          <t>0507-1409-7525</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 63 4층</t>
+          <t>경기도 고양시 일산동구 중앙로 1036 지하1층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/idhairsuho</t>
+          <t>http://junohair.com/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -6413,7 +6441,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6433,13 +6461,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>4587</v>
+        <v>14451</v>
       </c>
       <c r="Q64" t="n">
-        <v>507</v>
+        <v>1102</v>
       </c>
       <c r="R64" t="n">
-        <v>5094</v>
+        <v>15553</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6448,17 +6476,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1598173425</t>
+          <t>37865008</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598173425</t>
+          <t>https://m.place.naver.com/place/37865008</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6470,29 +6498,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>리안헤어 일산강선마을점</t>
+          <t>아이디헤어 덕이점</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>riahn0725@naver.com</t>
+          <t>0979012@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1386-2061</t>
+          <t>0507-1477-3303</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 상가동 2층</t>
+          <t>경기도 고양시 일산서구 하이파크3로 84 신성프라자 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/0979012</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6502,12 +6530,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6523,17 +6551,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>349</v>
+        <v>6377</v>
       </c>
       <c r="Q65" t="n">
-        <v>36</v>
+        <v>800</v>
       </c>
       <c r="R65" t="n">
-        <v>385</v>
+        <v>7177</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6542,17 +6570,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1577768619</t>
+          <t>1067110565</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1577768619</t>
+          <t>https://m.place.naver.com/place/1067110565</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6564,29 +6592,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>리안헤어 일산후곡마을점</t>
+          <t>벨유헤어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>riahn_hugok@naver.com</t>
+          <t>daisy952@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1447-6666</t>
+          <t>0507-1370-1915</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일산로 562 2층 206호</t>
+          <t>경기도 고양시 일산동구 율천로8번길 15-2 1층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/riahn_hugok</t>
+          <t>https://www.instagram.com/belleu_hair</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6601,7 +6629,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6621,13 +6649,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2658</v>
+        <v>425</v>
       </c>
       <c r="Q66" t="n">
-        <v>325</v>
+        <v>30</v>
       </c>
       <c r="R66" t="n">
-        <v>2983</v>
+        <v>455</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6636,17 +6664,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1249809757</t>
+          <t>1752531387</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1249809757</t>
+          <t>https://m.place.naver.com/place/1752531387</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6658,29 +6686,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>보그헤어 위시티점</t>
+          <t>아이디헤어 주엽2호점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>vog_wicity@naver.com</t>
+          <t>p2464610@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1317-3487</t>
+          <t>0507-1334-6477</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티2로11번길 45 상가 B동 210호</t>
+          <t>경기도 고양시 일산서구 중앙로 1444 태원빌딩 3층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vog_wicity</t>
+          <t>https://blog.naver.com/p2464610</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6715,13 +6743,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1618</v>
+        <v>13670</v>
       </c>
       <c r="Q67" t="n">
-        <v>180</v>
+        <v>5615</v>
       </c>
       <c r="R67" t="n">
-        <v>1798</v>
+        <v>19285</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6730,17 +6758,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1668585644</t>
+          <t>13321073</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1668585644</t>
+          <t>https://m.place.naver.com/place/13321073</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6752,43 +6780,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>아이디헤어 원마운트점</t>
+          <t>하인즈뷰티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2624280@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>idhairkorea@gmail.com</t>
-        </is>
-      </c>
+          <t>kimsuna1210@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1359-6700</t>
+          <t>0507-1489-8486</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 한류월드로 300 2층 아이디헤어 원마운트점</t>
+          <t>경기도 고양시 일산동구 정발산로 33 낙원프라자 2층 206호</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.idhair.com</t>
+          <t>https://blog.naver.com/kimsuna1210</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6813,13 +6837,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>26715</v>
+        <v>2301</v>
       </c>
       <c r="Q68" t="n">
-        <v>6332</v>
+        <v>477</v>
       </c>
       <c r="R68" t="n">
-        <v>33047</v>
+        <v>2778</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6828,17 +6852,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>32630576</t>
+          <t>37769980</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32630576</t>
+          <t>https://m.place.naver.com/place/37769980</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6850,29 +6874,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>리안헤어 일산중산동점</t>
+          <t>헤어디자인 상상 2호점</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>wlsdudlover@naver.com</t>
+          <t>assa807@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>031-977-3211</t>
+          <t>031-903-7897</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중산로 67</t>
+          <t>경기도 고양시 일산동구 강송로88번길 8-6 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kangkang2_2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6882,7 +6906,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -6903,17 +6927,17 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3483</v>
+        <v>862</v>
       </c>
       <c r="Q69" t="n">
-        <v>26</v>
+        <v>149</v>
       </c>
       <c r="R69" t="n">
-        <v>3509</v>
+        <v>1011</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6922,17 +6946,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1780881257</t>
+          <t>611759293</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1780881257</t>
+          <t>https://m.place.naver.com/place/611759293</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -6944,39 +6968,43 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>이철헤어커커 일산역점</t>
+          <t>두쏠헤어 이마트 풍산점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>yuntee_@naver.com</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>akmano@naver.com</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>cto@handsos.com</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1367-3175</t>
+          <t>0507-1420-7588</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 고양대로632번길 62 서원빌딩 2층 이철헤어커커</t>
+          <t>경기도 고양시 일산동구 무궁화로 237 이마트 풍산점 4층</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kerker3175?igsh=bjNmOXZ5eXhybzh4&amp;utm_source=qr</t>
+          <t>https://booking.naver.com/booking/13/bizes/415410</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6997,17 +7025,17 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1914</v>
+        <v>1604</v>
       </c>
       <c r="Q70" t="n">
-        <v>77</v>
+        <v>1143</v>
       </c>
       <c r="R70" t="n">
-        <v>1991</v>
+        <v>2747</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -7016,17 +7044,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1225883043</t>
+          <t>491005009</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1225883043</t>
+          <t>https://m.place.naver.com/place/491005009</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7038,29 +7066,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>그레이큐브</t>
+          <t>부티크아티산 백석점</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>thgus9800@naver.com</t>
+          <t>boutique_artisan@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1366-3237</t>
+          <t>0507-1344-2609</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 대산로11번길 5-15 1층</t>
+          <t>경기도 고양시 일산동구 호수로430번길 74-3 1층</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/greycube_hairsalon</t>
+          <t>http://instagram.com/artisan2_official</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7095,13 +7123,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1248</v>
+        <v>2110</v>
       </c>
       <c r="Q71" t="n">
-        <v>410</v>
+        <v>67</v>
       </c>
       <c r="R71" t="n">
-        <v>1658</v>
+        <v>2177</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7110,17 +7138,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1598823510</t>
+          <t>1731570285</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1598823510</t>
+          <t>https://m.place.naver.com/place/1731570285</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7132,43 +7160,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>두쏠헤어 이마트 풍산점</t>
+          <t>메종드아이디헤어 위시티점 1관</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>akmano@naver.com</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>cto@handsos.com</t>
-        </is>
-      </c>
+          <t>idhair01199@naver.com</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1420-7588</t>
+          <t>0507-1408-1654</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 무궁화로 237 이마트 풍산점 4층</t>
+          <t>경기도 고양시 일산동구 위시티2로11번길 31 스타타워1차 2층 아이디헤어</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/415410</t>
+          <t>https://www.instagram.com/idhair_wicity_official</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7189,17 +7213,17 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1564</v>
+        <v>3792</v>
       </c>
       <c r="Q72" t="n">
-        <v>1084</v>
+        <v>1474</v>
       </c>
       <c r="R72" t="n">
-        <v>2648</v>
+        <v>5266</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7208,17 +7232,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>491005009</t>
+          <t>35862167</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/491005009</t>
+          <t>https://m.place.naver.com/place/35862167</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7230,44 +7254,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>벨유헤어</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>daisy952@naver.com</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>아이디헤어 풍동점</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>idhairkorea@gmail.com</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1370-1915</t>
+          <t>0507-1344-1654</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 율천로8번길 15-2 1층</t>
+          <t>경기도 고양시 일산동구 숲속마을로 26 풍동프라자 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/belleu_hair</t>
+          <t>http://www.idhair.com/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7287,13 +7311,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>423</v>
+        <v>5387</v>
       </c>
       <c r="Q73" t="n">
-        <v>30</v>
+        <v>478</v>
       </c>
       <c r="R73" t="n">
-        <v>453</v>
+        <v>5865</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7302,17 +7326,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1752531387</t>
+          <t>658085259</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1752531387</t>
+          <t>https://m.place.naver.com/place/658085259</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7324,25 +7348,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>아이디헤어 라페스타점</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>그레이큐브</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>thgus9800@naver.com</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1374-0041</t>
+          <t>0507-1366-3237</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로1275번길 60-30 라페스타 B동 3F 315호</t>
+          <t>경기도 고양시 일산동구 대산로11번길 5-15 1층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/greycube_hairsalon</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7352,7 +7380,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -7373,17 +7401,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>6768</v>
+        <v>1258</v>
       </c>
       <c r="Q74" t="n">
-        <v>1299</v>
+        <v>414</v>
       </c>
       <c r="R74" t="n">
-        <v>8067</v>
+        <v>1672</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7392,51 +7420,51 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>11893440</t>
+          <t>1598823510</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11893440</t>
+          <t>https://m.place.naver.com/place/1598823510</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>미용실</t>
+          <t>이용원</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>무튼헤어 킨텍스점</t>
+          <t>바버샵 웰던 맨즈헤어</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ihair2@naver.com</t>
+          <t>ahrdudcks@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1315-5863</t>
+          <t>0507-1475-8263</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 킨텍스로 240 GIFC MALL 지하1층 143호 무튼</t>
+          <t>경기도 고양시 일산동구 중앙로1275번길 38-31 라페스타A동 1층 108호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/muten_hair</t>
+          <t>https://blog.naver.com/ahrdudcks</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7451,7 +7479,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7471,13 +7499,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>734</v>
+        <v>1445</v>
       </c>
       <c r="Q75" t="n">
-        <v>236</v>
+        <v>35</v>
       </c>
       <c r="R75" t="n">
-        <v>970</v>
+        <v>1480</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7486,17 +7514,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1104236533</t>
+          <t>1102477746</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1104236533</t>
+          <t>https://m.place.naver.com/place/1102477746</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -7565,13 +7593,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2378</v>
+        <v>2386</v>
       </c>
       <c r="Q76" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R76" t="n">
-        <v>2463</v>
+        <v>2473</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7590,7 +7618,7 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
